--- a/public/sampleFiles/service_user_sample_file.xlsx
+++ b/public/sampleFiles/service_user_sample_file.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\ThirdEx\sample files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Thirdex\thirdxui\public\sampleFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61669399-58EF-4C12-BE48-7B1AAC59663E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="87">
   <si>
     <t>personalInfo_title</t>
   </si>
@@ -84,36 +85,6 @@
   </si>
   <si>
     <t>demo, deo</t>
-  </si>
-  <si>
-    <t>campaigns one, campaigns two</t>
-  </si>
-  <si>
-    <t>Engagement two, Engagement one</t>
-  </si>
-  <si>
-    <t>event two, event one</t>
-  </si>
-  <si>
-    <t>funding two</t>
-  </si>
-  <si>
-    <t>otherInfo_benificiary_information</t>
-  </si>
-  <si>
-    <t>otherInfo_campaigns_supported</t>
-  </si>
-  <si>
-    <t>otherInfo_engagement</t>
-  </si>
-  <si>
-    <t>otherInfo_events_attended</t>
-  </si>
-  <si>
-    <t>otherInfo_funding_interests</t>
-  </si>
-  <si>
-    <t>otherInfo_fundraising_activities</t>
   </si>
   <si>
     <t>otherInfo_file</t>
@@ -314,12 +285,15 @@
   </si>
   <si>
     <t>phone</t>
+  </si>
+  <si>
+    <t>otherInfo_tags</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -645,38 +619,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BJ2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BE2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="3" max="3" width="21.88671875" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" customWidth="1"/>
-    <col min="7" max="7" width="17.88671875" customWidth="1"/>
-    <col min="8" max="8" width="21.109375" customWidth="1"/>
-    <col min="9" max="9" width="21.44140625" customWidth="1"/>
-    <col min="10" max="10" width="18.77734375" customWidth="1"/>
-    <col min="11" max="11" width="19.5546875" customWidth="1"/>
-    <col min="12" max="12" width="20.5546875" customWidth="1"/>
-    <col min="13" max="13" width="19.21875" customWidth="1"/>
-    <col min="14" max="14" width="17.21875" customWidth="1"/>
-    <col min="15" max="15" width="19.6640625" customWidth="1"/>
-    <col min="16" max="17" width="16.21875" customWidth="1"/>
-    <col min="18" max="18" width="18.6640625" customWidth="1"/>
-    <col min="19" max="19" width="17.88671875" customWidth="1"/>
-    <col min="20" max="20" width="25.77734375" customWidth="1"/>
-    <col min="27" max="27" width="14" customWidth="1"/>
-    <col min="34" max="34" width="16.33203125" customWidth="1"/>
-    <col min="45" max="45" width="13.6640625" customWidth="1"/>
-    <col min="46" max="46" width="14.77734375" customWidth="1"/>
-    <col min="49" max="49" width="15.21875" customWidth="1"/>
-    <col min="51" max="51" width="19.5546875" customWidth="1"/>
+    <col min="1" max="1" width="19.54296875" customWidth="1"/>
+    <col min="2" max="2" width="19.6328125" customWidth="1"/>
+    <col min="3" max="3" width="21.90625" customWidth="1"/>
+    <col min="4" max="4" width="20.453125" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" customWidth="1"/>
+    <col min="6" max="6" width="20.453125" customWidth="1"/>
+    <col min="7" max="7" width="17.90625" customWidth="1"/>
+    <col min="8" max="8" width="21.08984375" customWidth="1"/>
+    <col min="9" max="9" width="21.453125" customWidth="1"/>
+    <col min="10" max="10" width="18.81640625" customWidth="1"/>
+    <col min="11" max="11" width="19.54296875" customWidth="1"/>
+    <col min="12" max="12" width="20.54296875" customWidth="1"/>
+    <col min="13" max="13" width="19.1796875" customWidth="1"/>
+    <col min="14" max="14" width="17.1796875" customWidth="1"/>
+    <col min="15" max="15" width="19.6328125" customWidth="1"/>
+    <col min="16" max="17" width="16.1796875" customWidth="1"/>
+    <col min="18" max="18" width="18.6328125" customWidth="1"/>
+    <col min="19" max="19" width="17.90625" customWidth="1"/>
+    <col min="20" max="20" width="25.81640625" customWidth="1"/>
+    <col min="22" max="22" width="14" customWidth="1"/>
+    <col min="29" max="29" width="16.36328125" customWidth="1"/>
+    <col min="40" max="40" width="13.6328125" customWidth="1"/>
+    <col min="41" max="41" width="14.81640625" customWidth="1"/>
+    <col min="44" max="44" width="15.1796875" customWidth="1"/>
+    <col min="46" max="46" width="19.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:57" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,159 +709,144 @@
         <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AN1" t="s">
         <v>39</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BA1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:57" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>57</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" t="s">
         <v>58</v>
       </c>
-      <c r="BC1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="BD1" s="1" t="s">
+      <c r="D2" t="s">
         <v>60</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="E2" t="s">
         <v>61</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="F2" t="s">
         <v>62</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:62" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" t="s">
-        <v>72</v>
       </c>
       <c r="G2" s="2">
         <v>37439</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I2">
         <v>9384840388</v>
@@ -896,28 +855,28 @@
         <v>9384840388</v>
       </c>
       <c r="K2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="L2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="M2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="N2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="O2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="P2">
         <v>88484</v>
       </c>
       <c r="Q2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="R2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="S2">
         <v>8374</v>
@@ -926,136 +885,121 @@
         <v>19</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="W2" t="b">
+        <v>1</v>
+      </c>
+      <c r="X2" t="s">
+        <v>72</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="Z2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC2">
+        <v>9384840388</v>
+      </c>
+      <c r="AD2">
+        <v>9384840388</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ2">
+        <v>476522</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM2" t="s">
         <v>80</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AN2" s="2">
+        <v>45847</v>
+      </c>
+      <c r="AO2" s="2">
+        <v>45862</v>
+      </c>
+      <c r="AP2" t="s">
         <v>81</v>
       </c>
-      <c r="AB2" t="b">
+      <c r="AQ2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AR2">
+        <v>9384840388</v>
+      </c>
+      <c r="AS2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AT2">
+        <v>9384840388</v>
+      </c>
+      <c r="AU2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW2" s="2">
+        <v>45840</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AY2" s="2">
+        <v>45842</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>85</v>
+      </c>
+      <c r="BA2">
+        <v>9384840388</v>
+      </c>
+      <c r="BB2" t="b">
         <v>1</v>
       </c>
-      <c r="AC2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH2">
-        <v>9384840388</v>
-      </c>
-      <c r="AI2">
-        <v>9384840388</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AO2">
-        <v>476522</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AS2" s="2">
-        <v>45847</v>
-      </c>
-      <c r="AT2" s="2">
-        <v>45862</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AW2">
-        <v>9384840388</v>
-      </c>
-      <c r="AX2" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AY2">
-        <v>9384840388</v>
-      </c>
-      <c r="AZ2" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>94</v>
-      </c>
-      <c r="BB2" s="2">
-        <v>45840</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>95</v>
-      </c>
-      <c r="BD2" s="2">
-        <v>45842</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>95</v>
-      </c>
-      <c r="BF2">
-        <v>9384840388</v>
-      </c>
-      <c r="BG2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BH2" t="b">
+      <c r="BC2" t="b">
         <v>0</v>
       </c>
-      <c r="BI2" t="b">
+      <c r="BD2" t="b">
         <v>0</v>
       </c>
-      <c r="BJ2" t="b">
+      <c r="BE2" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AX2" r:id="rId1"/>
-    <hyperlink ref="AZ2" r:id="rId2"/>
+    <hyperlink ref="AS2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="AU2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId3"/>
